--- a/mlb_weather_professional_2026_07_12.xlsx
+++ b/mlb_weather_professional_2026_07_12.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="422">
   <si>
     <t>Date</t>
   </si>
@@ -716,61 +716,64 @@
     <t>Petco Park</t>
   </si>
   <si>
+    <t>🟨 Neutral</t>
+  </si>
+  <si>
+    <t>🟧 Below Average</t>
+  </si>
+  <si>
+    <t>🟢 Good</t>
+  </si>
+  <si>
     <t>🔥 Excellent</t>
   </si>
   <si>
-    <t>🚀 Elite</t>
-  </si>
-  <si>
-    <t>🟢 Good</t>
-  </si>
-  <si>
     <t>🟢 Very Good</t>
   </si>
   <si>
-    <t>adjusted carry 83.9; +19 ft carry; +8.1% HR env.; elevated delay risk 56</t>
-  </si>
-  <si>
-    <t>adjusted carry 83.8; +19 ft carry; +8.1% HR env.; elevated delay risk 53</t>
-  </si>
-  <si>
-    <t>adjusted carry 83.4; +18 ft carry; +8.0% HR env.; high delay risk 60</t>
-  </si>
-  <si>
-    <t>adjusted carry 82.3; +18 ft carry; +7.8% HR env.; high delay risk 72</t>
-  </si>
-  <si>
-    <t>adjusted carry 84.1; +19 ft carry; +8.2% HR env.; elevated delay risk 42</t>
-  </si>
-  <si>
-    <t>adjusted carry 90.2; +22 ft carry; +9.6% HR env.; elevated delay risk 60</t>
-  </si>
-  <si>
-    <t>adjusted carry 84.4; +19 ft carry; +8.3% HR env.; elevated delay risk 40</t>
-  </si>
-  <si>
-    <t>adjusted carry 90.6; +22 ft carry; +9.7% HR env.; high delay risk 64</t>
-  </si>
-  <si>
-    <t>adjusted carry 93.0; +24 ft carry; +10.3% HR env.; elevated delay risk 44</t>
-  </si>
-  <si>
-    <t>adjusted carry 80.3; +17 ft carry; +7.3% HR env.; elevated delay risk 56</t>
-  </si>
-  <si>
-    <t>adjusted carry 85.0; +19 ft carry; +8.4% HR env.; elevated delay risk 60</t>
-  </si>
-  <si>
-    <t>adjusted carry 93.0; +24 ft carry; +10.3% HR env.; elevated delay risk 49</t>
-  </si>
-  <si>
-    <t>adjusted carry 61.4; +6 ft carry; +2.7% HR env.; high delay risk 70</t>
-  </si>
-  <si>
-    <t>adjusted carry 84.7; +19 ft carry; +8.3% HR env.; elevated delay risk 53</t>
-  </si>
-  <si>
-    <t>adjusted carry 73.5; +13 ft carry; +5.6% HR env.; high delay risk 70</t>
+    <t>adjusted carry 56.5; +4 ft carry; +1.6% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 42.9; -4 ft carry; -1.7% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 48.9; -1 ft carry; -0.3% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 47.2; -2 ft carry; -0.7% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 66.8; +9 ft carry; +4.0% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 54.5; +2 ft carry; +1.1% HR env.; roof-controlled environment</t>
+  </si>
+  <si>
+    <t>adjusted carry 44.8; -3 ft carry; -1.2% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 54.9; +3 ft carry; +1.2% HR env.; roof-controlled environment</t>
+  </si>
+  <si>
+    <t>adjusted carry 88.4; +21 ft carry; +9.2% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 42.0; -4 ft carry; -1.9% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 42.3; -4 ft carry; -1.8% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 54.3; +2 ft carry; +1.0% HR env.; roof-controlled environment</t>
+  </si>
+  <si>
+    <t>adjusted carry 56.2; +3 ft carry; +1.5% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 76.7; +15 ft carry; +6.4% HR env.</t>
+  </si>
+  <si>
+    <t>adjusted carry 62.0; +7 ft carry; +2.9% HR env.</t>
   </si>
   <si>
     <t>73rd</t>
@@ -833,49 +836,46 @@
     <t>A-</t>
   </si>
   <si>
-    <t>2026-07-11 01:54:00 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:01 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:02 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:04 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:05 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:06 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:07 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:09 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:10 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:11 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:12 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:14 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:15 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:16 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-11 01:54:17 PM PDT</t>
+    <t>2026-07-11 01:55:42 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:55:43 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:55:44 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:55:45 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:55:46 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:55:47 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:55:48 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:55:49 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:55:50 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:55:51 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:55:52 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:55:53 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:55:54 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-11 01:55:55 PM PDT</t>
   </si>
   <si>
     <t>LOW</t>
@@ -941,49 +941,46 @@
     <t>Mostly clear</t>
   </si>
   <si>
-    <t>2026-07-11 20:54:00 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:01 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:02 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:04 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:05 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:06 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:07 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:09 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:10 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:11 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:12 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:14 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:15 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:16 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-11 20:54:17 UTC</t>
+    <t>2026-07-11 20:55:42 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:55:43 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:55:44 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:55:45 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:55:46 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:55:47 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:55:48 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:55:49 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:55:50 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:55:51 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:55:52 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:55:53 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:55:54 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-11 20:55:55 UTC</t>
   </si>
   <si>
     <t>2026-07-11T18:21:38+00:00</t>
@@ -1756,7 +1753,7 @@
     <col min="6" max="6" width="19.7109375" customWidth="1"/>
     <col min="7" max="7" width="29.7109375" customWidth="1"/>
     <col min="8" max="8" width="19.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
     <col min="10" max="10" width="34.7109375" customWidth="1"/>
     <col min="11" max="11" width="17.7109375" customWidth="1"/>
     <col min="12" max="12" width="27.7109375" customWidth="1"/>
@@ -2372,7 +2369,7 @@
         <v>231</v>
       </c>
       <c r="J2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K2">
         <v>57.2</v>
@@ -2381,10 +2378,10 @@
         <v>56.5</v>
       </c>
       <c r="M2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O2">
         <v>4</v>
@@ -2408,10 +2405,10 @@
         <v>1.017</v>
       </c>
       <c r="V2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="W2">
-        <v>152.4</v>
+        <v>154.1</v>
       </c>
       <c r="X2">
         <v>5</v>
@@ -2474,7 +2471,7 @@
         <v>306</v>
       </c>
       <c r="AR2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AS2">
         <v>0.92</v>
@@ -2552,7 +2549,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BR2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BS2">
         <v>-3.2</v>
@@ -2621,7 +2618,7 @@
         <v>9.5</v>
       </c>
       <c r="CO2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="CP2">
         <v>-3.5</v>
@@ -2690,7 +2687,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="DL2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="DM2">
         <v>-3.4</v>
@@ -2759,7 +2756,7 @@
         <v>10.3</v>
       </c>
       <c r="EI2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="EJ2">
         <v>-3.8</v>
@@ -2830,13 +2827,13 @@
         <v>217</v>
       </c>
       <c r="H3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K3">
         <v>41.8</v>
@@ -2845,10 +2842,10 @@
         <v>42.9</v>
       </c>
       <c r="M3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O3">
         <v>-4</v>
@@ -2872,10 +2869,10 @@
         <v>0.981</v>
       </c>
       <c r="V3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="W3">
-        <v>150.9</v>
+        <v>152.6</v>
       </c>
       <c r="X3">
         <v>5</v>
@@ -2938,7 +2935,7 @@
         <v>307</v>
       </c>
       <c r="AR3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AS3">
         <v>0.92</v>
@@ -3016,7 +3013,7 @@
         <v>13.3</v>
       </c>
       <c r="BR3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BS3">
         <v>-6.6</v>
@@ -3085,7 +3082,7 @@
         <v>13.1</v>
       </c>
       <c r="CO3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="CP3">
         <v>-6.6</v>
@@ -3154,7 +3151,7 @@
         <v>13</v>
       </c>
       <c r="DL3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="DM3">
         <v>-7.1</v>
@@ -3223,7 +3220,7 @@
         <v>13.2</v>
       </c>
       <c r="EI3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="EJ3">
         <v>-7.3</v>
@@ -3294,13 +3291,13 @@
         <v>218</v>
       </c>
       <c r="H4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K4">
         <v>48.8</v>
@@ -3309,10 +3306,10 @@
         <v>48.9</v>
       </c>
       <c r="M4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -3336,10 +3333,10 @@
         <v>0.997</v>
       </c>
       <c r="V4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="W4">
-        <v>150.9</v>
+        <v>152.6</v>
       </c>
       <c r="X4">
         <v>5</v>
@@ -3402,7 +3399,7 @@
         <v>308</v>
       </c>
       <c r="AR4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AS4">
         <v>0.92</v>
@@ -3480,7 +3477,7 @@
         <v>13.3</v>
       </c>
       <c r="BR4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BS4">
         <v>-4.2</v>
@@ -3549,7 +3546,7 @@
         <v>14</v>
       </c>
       <c r="CO4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="CP4">
         <v>-4.5</v>
@@ -3618,7 +3615,7 @@
         <v>14.5</v>
       </c>
       <c r="DL4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="DM4">
         <v>-4.6</v>
@@ -3687,7 +3684,7 @@
         <v>14.7</v>
       </c>
       <c r="EI4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="EJ4">
         <v>-4.7</v>
@@ -3758,13 +3755,13 @@
         <v>219</v>
       </c>
       <c r="H5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K5">
         <v>46.8</v>
@@ -3773,10 +3770,10 @@
         <v>47.2</v>
       </c>
       <c r="M5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O5">
         <v>-2</v>
@@ -3800,10 +3797,10 @@
         <v>0.992</v>
       </c>
       <c r="V5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="W5">
-        <v>53.4</v>
+        <v>55.1</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -3866,7 +3863,7 @@
         <v>309</v>
       </c>
       <c r="AR5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AS5">
         <v>1</v>
@@ -3944,7 +3941,7 @@
         <v>15.4</v>
       </c>
       <c r="BR5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BS5">
         <v>-7.5</v>
@@ -4013,7 +4010,7 @@
         <v>15.5</v>
       </c>
       <c r="CO5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="CP5">
         <v>-6.8</v>
@@ -4082,7 +4079,7 @@
         <v>15.5</v>
       </c>
       <c r="DL5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="DM5">
         <v>-6.5</v>
@@ -4151,7 +4148,7 @@
         <v>15.8</v>
       </c>
       <c r="EI5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="EJ5">
         <v>-7.1</v>
@@ -4222,13 +4219,13 @@
         <v>220</v>
       </c>
       <c r="H6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K6">
         <v>68.5</v>
@@ -4237,10 +4234,10 @@
         <v>66.8</v>
       </c>
       <c r="M6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O6">
         <v>9</v>
@@ -4264,10 +4261,10 @@
         <v>1.045</v>
       </c>
       <c r="V6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="W6">
-        <v>39.1</v>
+        <v>40.8</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -4330,7 +4327,7 @@
         <v>310</v>
       </c>
       <c r="AR6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AS6">
         <v>0.92</v>
@@ -4408,7 +4405,7 @@
         <v>7.8</v>
       </c>
       <c r="BR6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="BS6">
         <v>1.8</v>
@@ -4477,7 +4474,7 @@
         <v>11.3</v>
       </c>
       <c r="CO6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="CP6">
         <v>2.6</v>
@@ -4546,7 +4543,7 @@
         <v>13</v>
       </c>
       <c r="DL6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="DM6">
         <v>3.1</v>
@@ -4615,7 +4612,7 @@
         <v>14.1</v>
       </c>
       <c r="EI6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="EJ6">
         <v>7.6</v>
@@ -4686,13 +4683,13 @@
         <v>221</v>
       </c>
       <c r="H7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K7">
         <v>55.2</v>
@@ -4701,10 +4698,10 @@
         <v>54.5</v>
       </c>
       <c r="M7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O7">
         <v>2</v>
@@ -4728,10 +4725,10 @@
         <v>1.013</v>
       </c>
       <c r="V7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="W7">
-        <v>97.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -4794,7 +4791,7 @@
         <v>311</v>
       </c>
       <c r="AR7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AS7">
         <v>0.92</v>
@@ -4872,7 +4869,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="BR7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="BS7">
         <v>0</v>
@@ -4941,7 +4938,7 @@
         <v>6.8</v>
       </c>
       <c r="CO7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="CP7">
         <v>0</v>
@@ -5010,7 +5007,7 @@
         <v>7.4</v>
       </c>
       <c r="DL7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="DM7">
         <v>0</v>
@@ -5079,7 +5076,7 @@
         <v>10.2</v>
       </c>
       <c r="EI7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="EJ7">
         <v>0</v>
@@ -5150,13 +5147,13 @@
         <v>222</v>
       </c>
       <c r="H8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K8">
         <v>44.4</v>
@@ -5165,10 +5162,10 @@
         <v>44.8</v>
       </c>
       <c r="M8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O8">
         <v>-3</v>
@@ -5195,7 +5192,7 @@
         <v>276</v>
       </c>
       <c r="W8">
-        <v>29.4</v>
+        <v>31.1</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -5255,10 +5252,10 @@
         <v>302</v>
       </c>
       <c r="AQ8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AR8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AS8">
         <v>0.92</v>
@@ -5336,7 +5333,7 @@
         <v>13.5</v>
       </c>
       <c r="BR8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="BS8">
         <v>-7.3</v>
@@ -5405,7 +5402,7 @@
         <v>14</v>
       </c>
       <c r="CO8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="CP8">
         <v>-7.5</v>
@@ -5474,7 +5471,7 @@
         <v>13.5</v>
       </c>
       <c r="DL8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="DM8">
         <v>-7.3</v>
@@ -5543,7 +5540,7 @@
         <v>13.4</v>
       </c>
       <c r="EI8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="EJ8">
         <v>-7.2</v>
@@ -5614,13 +5611,13 @@
         <v>223</v>
       </c>
       <c r="H9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K9">
         <v>55.2</v>
@@ -5629,10 +5626,10 @@
         <v>54.9</v>
       </c>
       <c r="M9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O9">
         <v>3</v>
@@ -5659,7 +5656,7 @@
         <v>277</v>
       </c>
       <c r="W9">
-        <v>37.2</v>
+        <v>38.8</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -5719,10 +5716,10 @@
         <v>302</v>
       </c>
       <c r="AQ9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AR9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AS9">
         <v>0.92</v>
@@ -5800,7 +5797,7 @@
         <v>10.5</v>
       </c>
       <c r="BR9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BS9">
         <v>-0</v>
@@ -5869,7 +5866,7 @@
         <v>12.5</v>
       </c>
       <c r="CO9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="CP9">
         <v>0</v>
@@ -5938,7 +5935,7 @@
         <v>13.9</v>
       </c>
       <c r="DL9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="DM9">
         <v>0</v>
@@ -6007,7 +6004,7 @@
         <v>14.1</v>
       </c>
       <c r="EI9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="EJ9">
         <v>0</v>
@@ -6078,13 +6075,13 @@
         <v>224</v>
       </c>
       <c r="H10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K10">
         <v>92.2</v>
@@ -6093,10 +6090,10 @@
         <v>88.40000000000001</v>
       </c>
       <c r="M10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O10">
         <v>21</v>
@@ -6123,7 +6120,7 @@
         <v>278</v>
       </c>
       <c r="W10">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -6150,7 +6147,7 @@
         <v>285</v>
       </c>
       <c r="AF10">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="AG10" t="s">
         <v>289</v>
@@ -6183,10 +6180,10 @@
         <v>302</v>
       </c>
       <c r="AQ10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AR10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AS10">
         <v>0.92</v>
@@ -6264,7 +6261,7 @@
         <v>14.4</v>
       </c>
       <c r="BR10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="BS10">
         <v>8.199999999999999</v>
@@ -6333,7 +6330,7 @@
         <v>14.7</v>
       </c>
       <c r="CO10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="CP10">
         <v>8.4</v>
@@ -6402,7 +6399,7 @@
         <v>14.6</v>
       </c>
       <c r="DL10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="DM10">
         <v>8.4</v>
@@ -6471,7 +6468,7 @@
         <v>14.4</v>
       </c>
       <c r="EI10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="EJ10">
         <v>7.6</v>
@@ -6542,13 +6539,13 @@
         <v>225</v>
       </c>
       <c r="H11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K11">
         <v>40.6</v>
@@ -6557,10 +6554,10 @@
         <v>42</v>
       </c>
       <c r="M11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O11">
         <v>-4</v>
@@ -6587,7 +6584,7 @@
         <v>279</v>
       </c>
       <c r="W11">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -6647,10 +6644,10 @@
         <v>302</v>
       </c>
       <c r="AQ11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AR11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AS11">
         <v>0.92</v>
@@ -6728,7 +6725,7 @@
         <v>14.3</v>
       </c>
       <c r="BR11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BS11">
         <v>-7.7</v>
@@ -6797,7 +6794,7 @@
         <v>15.2</v>
       </c>
       <c r="CO11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="CP11">
         <v>-7.9</v>
@@ -6866,7 +6863,7 @@
         <v>15.8</v>
       </c>
       <c r="DL11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="DM11">
         <v>-8.1</v>
@@ -6935,7 +6932,7 @@
         <v>15.7</v>
       </c>
       <c r="EI11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="EJ11">
         <v>-8</v>
@@ -7006,13 +7003,13 @@
         <v>226</v>
       </c>
       <c r="H12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K12">
         <v>41.6</v>
@@ -7021,10 +7018,10 @@
         <v>42.3</v>
       </c>
       <c r="M12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O12">
         <v>-4</v>
@@ -7051,7 +7048,7 @@
         <v>280</v>
       </c>
       <c r="W12">
-        <v>52.3</v>
+        <v>54</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -7111,10 +7108,10 @@
         <v>304</v>
       </c>
       <c r="AQ12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AR12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AS12">
         <v>0.92</v>
@@ -7192,7 +7189,7 @@
         <v>14.2</v>
       </c>
       <c r="BR12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BS12">
         <v>-8.1</v>
@@ -7225,7 +7222,7 @@
         <v>42.3</v>
       </c>
       <c r="CC12">
-        <v>92.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="CD12">
         <v>5.9</v>
@@ -7261,7 +7258,7 @@
         <v>14.3</v>
       </c>
       <c r="CO12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="CP12">
         <v>-8.4</v>
@@ -7330,7 +7327,7 @@
         <v>14.7</v>
       </c>
       <c r="DL12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="DM12">
         <v>-8.6</v>
@@ -7399,7 +7396,7 @@
         <v>15.1</v>
       </c>
       <c r="EI12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="EJ12">
         <v>-8.800000000000001</v>
@@ -7470,13 +7467,13 @@
         <v>227</v>
       </c>
       <c r="H13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K13">
         <v>55.2</v>
@@ -7485,10 +7482,10 @@
         <v>54.3</v>
       </c>
       <c r="M13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O13">
         <v>2</v>
@@ -7515,7 +7512,7 @@
         <v>281</v>
       </c>
       <c r="W13">
-        <v>147.5</v>
+        <v>149.2</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -7575,10 +7572,10 @@
         <v>300</v>
       </c>
       <c r="AQ13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AR13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AS13">
         <v>0.92</v>
@@ -7656,7 +7653,7 @@
         <v>7.3</v>
       </c>
       <c r="BR13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BS13">
         <v>-0</v>
@@ -7725,7 +7722,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="CO13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="CP13">
         <v>0</v>
@@ -7794,7 +7791,7 @@
         <v>8.5</v>
       </c>
       <c r="DL13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="DM13">
         <v>-0</v>
@@ -7863,7 +7860,7 @@
         <v>9.1</v>
       </c>
       <c r="EI13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="EJ13">
         <v>0</v>
@@ -7934,13 +7931,13 @@
         <v>228</v>
       </c>
       <c r="H14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K14">
         <v>57.2</v>
@@ -7949,10 +7946,10 @@
         <v>56.2</v>
       </c>
       <c r="M14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O14">
         <v>3</v>
@@ -7979,7 +7976,7 @@
         <v>282</v>
       </c>
       <c r="W14">
-        <v>27.8</v>
+        <v>29.4</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -8039,10 +8036,10 @@
         <v>303</v>
       </c>
       <c r="AQ14" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AR14" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AS14">
         <v>0.82</v>
@@ -8120,7 +8117,7 @@
         <v>13.7</v>
       </c>
       <c r="BR14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="BS14">
         <v>5.8</v>
@@ -8189,7 +8186,7 @@
         <v>13</v>
       </c>
       <c r="CO14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="CP14">
         <v>5.2</v>
@@ -8258,7 +8255,7 @@
         <v>12.5</v>
       </c>
       <c r="DL14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="DM14">
         <v>5.5</v>
@@ -8327,7 +8324,7 @@
         <v>12.8</v>
       </c>
       <c r="EI14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="EJ14">
         <v>5.1</v>
@@ -8398,13 +8395,13 @@
         <v>229</v>
       </c>
       <c r="H15" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="I15" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="J15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K15">
         <v>81.3</v>
@@ -8413,10 +8410,10 @@
         <v>76.7</v>
       </c>
       <c r="M15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O15">
         <v>15</v>
@@ -8443,7 +8440,7 @@
         <v>283</v>
       </c>
       <c r="W15">
-        <v>96.3</v>
+        <v>98</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -8503,10 +8500,10 @@
         <v>303</v>
       </c>
       <c r="AQ15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AR15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AS15">
         <v>0.78</v>
@@ -8584,7 +8581,7 @@
         <v>8.9</v>
       </c>
       <c r="BR15" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="BS15">
         <v>5.8</v>
@@ -8653,7 +8650,7 @@
         <v>10.1</v>
       </c>
       <c r="CO15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="CP15">
         <v>6.2</v>
@@ -8722,7 +8719,7 @@
         <v>11</v>
       </c>
       <c r="DL15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="DM15">
         <v>6.5</v>
@@ -8791,7 +8788,7 @@
         <v>13</v>
       </c>
       <c r="EI15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="EJ15">
         <v>7.1</v>
@@ -8821,7 +8818,7 @@
         <v>80.7</v>
       </c>
       <c r="ES15">
-        <v>75.7</v>
+        <v>75.8</v>
       </c>
       <c r="ET15">
         <v>79.3</v>
@@ -8862,13 +8859,13 @@
         <v>230</v>
       </c>
       <c r="H16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J16" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K16">
         <v>63.7</v>
@@ -8877,10 +8874,10 @@
         <v>62</v>
       </c>
       <c r="M16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O16">
         <v>7</v>
@@ -8907,7 +8904,7 @@
         <v>284</v>
       </c>
       <c r="W16">
-        <v>148.1</v>
+        <v>149.7</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -8967,10 +8964,10 @@
         <v>305</v>
       </c>
       <c r="AQ16" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AR16" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AS16">
         <v>0.86</v>
@@ -9048,7 +9045,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="BR16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="BS16">
         <v>3</v>
@@ -9117,7 +9114,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="CO16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="CP16">
         <v>4.3</v>
@@ -9186,7 +9183,7 @@
         <v>10.2</v>
       </c>
       <c r="DL16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="DM16">
         <v>4.4</v>
@@ -9255,7 +9252,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="EI16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="EJ16">
         <v>4.3</v>
@@ -9411,10 +9408,10 @@
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>345</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>42</v>
@@ -9429,28 +9426,28 @@
         <v>22</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>23</v>
       </c>
       <c r="M1" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>351</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>352</v>
       </c>
       <c r="S1" s="3" t="s">
         <v>44</v>
@@ -9462,109 +9459,109 @@
         <v>46</v>
       </c>
       <c r="V1" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="W1" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AV1" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AW1" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AX1" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AY1" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="BA1" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BB1" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BC1" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BD1" s="3" t="s">
         <v>386</v>
-      </c>
-      <c r="BD1" s="3" t="s">
-        <v>387</v>
       </c>
       <c r="BE1" s="3" t="s">
         <v>31</v>
@@ -9573,16 +9570,16 @@
         <v>30</v>
       </c>
       <c r="BG1" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="BH1" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="BH1" s="3" t="s">
+      <c r="BI1" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="BI1" s="3" t="s">
+      <c r="BJ1" s="3" t="s">
         <v>390</v>
-      </c>
-      <c r="BJ1" s="3" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:62">
@@ -9599,7 +9596,7 @@
         <v>216</v>
       </c>
       <c r="E2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F2" t="s">
         <v>208</v>
@@ -9608,13 +9605,13 @@
         <v>306</v>
       </c>
       <c r="H2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J2">
-        <v>152.4</v>
+        <v>154.1</v>
       </c>
       <c r="K2">
         <v>19.3</v>
@@ -9695,7 +9692,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AK2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL2">
         <v>90</v>
@@ -9716,7 +9713,7 @@
         <v>1.1347</v>
       </c>
       <c r="AR2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS2">
         <v>2359</v>
@@ -9787,22 +9784,22 @@
         <v>216</v>
       </c>
       <c r="E3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G3" t="s">
         <v>306</v>
       </c>
       <c r="H3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J3">
-        <v>152.4</v>
+        <v>154.1</v>
       </c>
       <c r="K3">
         <v>20.3</v>
@@ -9883,7 +9880,7 @@
         <v>9.5</v>
       </c>
       <c r="AK3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL3">
         <v>90</v>
@@ -9904,7 +9901,7 @@
         <v>1.1312</v>
       </c>
       <c r="AR3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS3">
         <v>2482</v>
@@ -9975,22 +9972,22 @@
         <v>216</v>
       </c>
       <c r="E4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G4" t="s">
         <v>306</v>
       </c>
       <c r="H4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J4">
-        <v>152.4</v>
+        <v>154.1</v>
       </c>
       <c r="K4">
         <v>21.3</v>
@@ -10071,7 +10068,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AK4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL4">
         <v>90</v>
@@ -10092,7 +10089,7 @@
         <v>1.1284</v>
       </c>
       <c r="AR4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS4">
         <v>2577</v>
@@ -10163,22 +10160,22 @@
         <v>216</v>
       </c>
       <c r="E5" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G5" t="s">
         <v>306</v>
       </c>
       <c r="H5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J5">
-        <v>152.4</v>
+        <v>154.1</v>
       </c>
       <c r="K5">
         <v>22.3</v>
@@ -10259,7 +10256,7 @@
         <v>10.3</v>
       </c>
       <c r="AK5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL5">
         <v>90</v>
@@ -10280,7 +10277,7 @@
         <v>1.1267</v>
       </c>
       <c r="AR5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS5">
         <v>2639</v>
@@ -10351,7 +10348,7 @@
         <v>217</v>
       </c>
       <c r="E6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F6" t="s">
         <v>209</v>
@@ -10360,13 +10357,13 @@
         <v>307</v>
       </c>
       <c r="H6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J6">
-        <v>150.9</v>
+        <v>152.6</v>
       </c>
       <c r="K6">
         <v>20.7</v>
@@ -10447,7 +10444,7 @@
         <v>13.3</v>
       </c>
       <c r="AK6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL6">
         <v>90</v>
@@ -10468,7 +10465,7 @@
         <v>1.1677</v>
       </c>
       <c r="AR6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS6">
         <v>1402</v>
@@ -10539,22 +10536,22 @@
         <v>217</v>
       </c>
       <c r="E7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G7" t="s">
         <v>307</v>
       </c>
       <c r="H7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J7">
-        <v>150.9</v>
+        <v>152.6</v>
       </c>
       <c r="K7">
         <v>21.7</v>
@@ -10635,7 +10632,7 @@
         <v>13.1</v>
       </c>
       <c r="AK7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL7">
         <v>90</v>
@@ -10656,7 +10653,7 @@
         <v>1.166</v>
       </c>
       <c r="AR7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS7">
         <v>1465</v>
@@ -10727,22 +10724,22 @@
         <v>217</v>
       </c>
       <c r="E8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F8" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G8" t="s">
         <v>307</v>
       </c>
       <c r="H8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J8">
-        <v>150.9</v>
+        <v>152.6</v>
       </c>
       <c r="K8">
         <v>22.7</v>
@@ -10823,7 +10820,7 @@
         <v>13</v>
       </c>
       <c r="AK8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL8">
         <v>90</v>
@@ -10844,7 +10841,7 @@
         <v>1.1639</v>
       </c>
       <c r="AR8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS8">
         <v>1537</v>
@@ -10915,22 +10912,22 @@
         <v>217</v>
       </c>
       <c r="E9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G9" t="s">
         <v>307</v>
       </c>
       <c r="H9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J9">
-        <v>150.9</v>
+        <v>152.6</v>
       </c>
       <c r="K9">
         <v>23.7</v>
@@ -11011,7 +11008,7 @@
         <v>13.2</v>
       </c>
       <c r="AK9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL9">
         <v>90</v>
@@ -11032,7 +11029,7 @@
         <v>1.1658</v>
       </c>
       <c r="AR9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS9">
         <v>1490</v>
@@ -11103,7 +11100,7 @@
         <v>218</v>
       </c>
       <c r="E10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F10" t="s">
         <v>209</v>
@@ -11112,13 +11109,13 @@
         <v>308</v>
       </c>
       <c r="H10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J10">
-        <v>150.9</v>
+        <v>152.6</v>
       </c>
       <c r="K10">
         <v>20.7</v>
@@ -11199,7 +11196,7 @@
         <v>13.3</v>
       </c>
       <c r="AK10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL10">
         <v>90</v>
@@ -11220,7 +11217,7 @@
         <v>1.164</v>
       </c>
       <c r="AR10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS10">
         <v>1484</v>
@@ -11291,22 +11288,22 @@
         <v>218</v>
       </c>
       <c r="E11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G11" t="s">
         <v>308</v>
       </c>
       <c r="H11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J11">
-        <v>150.9</v>
+        <v>152.6</v>
       </c>
       <c r="K11">
         <v>21.7</v>
@@ -11387,7 +11384,7 @@
         <v>14</v>
       </c>
       <c r="AK11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL11">
         <v>90</v>
@@ -11408,7 +11405,7 @@
         <v>1.1633</v>
       </c>
       <c r="AR11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS11">
         <v>1518</v>
@@ -11479,22 +11476,22 @@
         <v>218</v>
       </c>
       <c r="E12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G12" t="s">
         <v>308</v>
       </c>
       <c r="H12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J12">
-        <v>150.9</v>
+        <v>152.6</v>
       </c>
       <c r="K12">
         <v>22.7</v>
@@ -11575,7 +11572,7 @@
         <v>14.5</v>
       </c>
       <c r="AK12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL12">
         <v>90</v>
@@ -11596,7 +11593,7 @@
         <v>1.1615</v>
       </c>
       <c r="AR12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS12">
         <v>1577</v>
@@ -11667,22 +11664,22 @@
         <v>218</v>
       </c>
       <c r="E13" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F13" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G13" t="s">
         <v>308</v>
       </c>
       <c r="H13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J13">
-        <v>150.9</v>
+        <v>152.6</v>
       </c>
       <c r="K13">
         <v>23.7</v>
@@ -11763,7 +11760,7 @@
         <v>14.7</v>
       </c>
       <c r="AK13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL13">
         <v>90</v>
@@ -11784,7 +11781,7 @@
         <v>1.1641</v>
       </c>
       <c r="AR13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS13">
         <v>1504</v>
@@ -11855,7 +11852,7 @@
         <v>219</v>
       </c>
       <c r="E14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F14" t="s">
         <v>210</v>
@@ -11864,16 +11861,16 @@
         <v>309</v>
       </c>
       <c r="H14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I14" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J14">
-        <v>53.4</v>
+        <v>55.1</v>
       </c>
       <c r="K14">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -11951,7 +11948,7 @@
         <v>15.4</v>
       </c>
       <c r="AK14" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL14">
         <v>45</v>
@@ -11972,7 +11969,7 @@
         <v>1.1403</v>
       </c>
       <c r="AR14" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS14">
         <v>2149</v>
@@ -12011,7 +12008,7 @@
         <v>286</v>
       </c>
       <c r="BE14">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="BF14" t="s">
         <v>285</v>
@@ -12043,25 +12040,25 @@
         <v>219</v>
       </c>
       <c r="E15" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F15" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G15" t="s">
         <v>309</v>
       </c>
       <c r="H15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J15">
-        <v>53.4</v>
+        <v>55.1</v>
       </c>
       <c r="K15">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -12139,7 +12136,7 @@
         <v>15.5</v>
       </c>
       <c r="AK15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL15">
         <v>45</v>
@@ -12160,7 +12157,7 @@
         <v>1.1397</v>
       </c>
       <c r="AR15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS15">
         <v>2165</v>
@@ -12231,25 +12228,25 @@
         <v>219</v>
       </c>
       <c r="E16" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F16" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G16" t="s">
         <v>309</v>
       </c>
       <c r="H16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I16" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J16">
-        <v>53.4</v>
+        <v>55.1</v>
       </c>
       <c r="K16">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -12327,7 +12324,7 @@
         <v>15.5</v>
       </c>
       <c r="AK16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL16">
         <v>45</v>
@@ -12348,7 +12345,7 @@
         <v>1.1397</v>
       </c>
       <c r="AR16" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS16">
         <v>2167</v>
@@ -12419,25 +12416,25 @@
         <v>219</v>
       </c>
       <c r="E17" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F17" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G17" t="s">
         <v>309</v>
       </c>
       <c r="H17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I17" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J17">
-        <v>53.4</v>
+        <v>55.1</v>
       </c>
       <c r="K17">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -12515,7 +12512,7 @@
         <v>15.8</v>
       </c>
       <c r="AK17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL17">
         <v>45</v>
@@ -12536,7 +12533,7 @@
         <v>1.1395</v>
       </c>
       <c r="AR17" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS17">
         <v>2169</v>
@@ -12607,7 +12604,7 @@
         <v>220</v>
       </c>
       <c r="E18" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F18" t="s">
         <v>210</v>
@@ -12616,16 +12613,16 @@
         <v>310</v>
       </c>
       <c r="H18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I18" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J18">
-        <v>39.1</v>
+        <v>40.8</v>
       </c>
       <c r="K18">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -12703,7 +12700,7 @@
         <v>7.8</v>
       </c>
       <c r="AK18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AL18">
         <v>135</v>
@@ -12724,7 +12721,7 @@
         <v>1.1666</v>
       </c>
       <c r="AR18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS18">
         <v>1517</v>
@@ -12795,25 +12792,25 @@
         <v>220</v>
       </c>
       <c r="E19" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F19" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G19" t="s">
         <v>310</v>
       </c>
       <c r="H19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J19">
-        <v>39.1</v>
+        <v>40.8</v>
       </c>
       <c r="K19">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -12891,7 +12888,7 @@
         <v>11.3</v>
       </c>
       <c r="AK19" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AL19">
         <v>135</v>
@@ -12912,7 +12909,7 @@
         <v>1.1677</v>
       </c>
       <c r="AR19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS19">
         <v>1458</v>
@@ -12983,25 +12980,25 @@
         <v>220</v>
       </c>
       <c r="E20" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F20" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G20" t="s">
         <v>310</v>
       </c>
       <c r="H20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J20">
-        <v>39.1</v>
+        <v>40.8</v>
       </c>
       <c r="K20">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -13079,7 +13076,7 @@
         <v>13</v>
       </c>
       <c r="AK20" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AL20">
         <v>135</v>
@@ -13100,7 +13097,7 @@
         <v>1.1694</v>
       </c>
       <c r="AR20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS20">
         <v>1418</v>
@@ -13171,25 +13168,25 @@
         <v>220</v>
       </c>
       <c r="E21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F21" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G21" t="s">
         <v>310</v>
       </c>
       <c r="H21" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J21">
-        <v>39.1</v>
+        <v>40.8</v>
       </c>
       <c r="K21">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -13267,7 +13264,7 @@
         <v>14.1</v>
       </c>
       <c r="AK21" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AL21">
         <v>180</v>
@@ -13288,7 +13285,7 @@
         <v>1.1715</v>
       </c>
       <c r="AR21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS21">
         <v>1362</v>
@@ -13359,7 +13356,7 @@
         <v>221</v>
       </c>
       <c r="E22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F22" t="s">
         <v>210</v>
@@ -13368,16 +13365,16 @@
         <v>311</v>
       </c>
       <c r="H22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I22" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J22">
-        <v>97.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="K22">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L22">
         <v>5</v>
@@ -13455,7 +13452,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="AK22" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AL22">
         <v>247.5</v>
@@ -13476,7 +13473,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR22" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS22">
         <v>858</v>
@@ -13547,25 +13544,25 @@
         <v>221</v>
       </c>
       <c r="E23" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F23" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G23" t="s">
         <v>311</v>
       </c>
       <c r="H23" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J23">
-        <v>97.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="K23">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="L23">
         <v>5</v>
@@ -13643,7 +13640,7 @@
         <v>6.8</v>
       </c>
       <c r="AK23" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AL23">
         <v>247.5</v>
@@ -13664,7 +13661,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS23">
         <v>858</v>
@@ -13735,25 +13732,25 @@
         <v>221</v>
       </c>
       <c r="E24" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F24" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G24" t="s">
         <v>311</v>
       </c>
       <c r="H24" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I24" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J24">
-        <v>97.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="K24">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="L24">
         <v>5</v>
@@ -13831,7 +13828,7 @@
         <v>7.4</v>
       </c>
       <c r="AK24" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AL24">
         <v>270</v>
@@ -13852,7 +13849,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR24" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS24">
         <v>858</v>
@@ -13923,25 +13920,25 @@
         <v>221</v>
       </c>
       <c r="E25" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F25" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G25" t="s">
         <v>311</v>
       </c>
       <c r="H25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I25" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J25">
-        <v>97.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="K25">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -14019,7 +14016,7 @@
         <v>10.2</v>
       </c>
       <c r="AK25" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AL25">
         <v>270</v>
@@ -14040,7 +14037,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR25" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS25">
         <v>858</v>
@@ -14111,25 +14108,25 @@
         <v>222</v>
       </c>
       <c r="E26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F26" t="s">
         <v>210</v>
       </c>
       <c r="G26" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H26" t="s">
         <v>276</v>
       </c>
       <c r="I26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J26">
-        <v>29.4</v>
+        <v>31.1</v>
       </c>
       <c r="K26">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -14207,7 +14204,7 @@
         <v>13.5</v>
       </c>
       <c r="AK26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AL26">
         <v>67.5</v>
@@ -14228,7 +14225,7 @@
         <v>1.1463</v>
       </c>
       <c r="AR26" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS26">
         <v>2103</v>
@@ -14299,25 +14296,25 @@
         <v>222</v>
       </c>
       <c r="E27" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F27" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G27" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H27" t="s">
         <v>276</v>
       </c>
       <c r="I27" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J27">
-        <v>29.4</v>
+        <v>31.1</v>
       </c>
       <c r="K27">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -14395,7 +14392,7 @@
         <v>14</v>
       </c>
       <c r="AK27" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AL27">
         <v>67.5</v>
@@ -14416,7 +14413,7 @@
         <v>1.1447</v>
       </c>
       <c r="AR27" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS27">
         <v>2161</v>
@@ -14487,25 +14484,25 @@
         <v>222</v>
       </c>
       <c r="E28" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F28" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H28" t="s">
         <v>276</v>
       </c>
       <c r="I28" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J28">
-        <v>29.4</v>
+        <v>31.1</v>
       </c>
       <c r="K28">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="L28">
         <v>5</v>
@@ -14583,7 +14580,7 @@
         <v>13.5</v>
       </c>
       <c r="AK28" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AL28">
         <v>67.5</v>
@@ -14604,7 +14601,7 @@
         <v>1.1444</v>
       </c>
       <c r="AR28" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS28">
         <v>2171</v>
@@ -14675,25 +14672,25 @@
         <v>222</v>
       </c>
       <c r="E29" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F29" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G29" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H29" t="s">
         <v>276</v>
       </c>
       <c r="I29" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J29">
-        <v>29.4</v>
+        <v>31.1</v>
       </c>
       <c r="K29">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -14771,7 +14768,7 @@
         <v>13.4</v>
       </c>
       <c r="AK29" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AL29">
         <v>67.5</v>
@@ -14792,7 +14789,7 @@
         <v>1.1443</v>
       </c>
       <c r="AR29" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS29">
         <v>2171</v>
@@ -14863,25 +14860,25 @@
         <v>223</v>
       </c>
       <c r="E30" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F30" t="s">
         <v>210</v>
       </c>
       <c r="G30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H30" t="s">
         <v>277</v>
       </c>
       <c r="I30" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J30">
-        <v>37.2</v>
+        <v>38.8</v>
       </c>
       <c r="K30">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L30">
         <v>5</v>
@@ -14959,7 +14956,7 @@
         <v>10.5</v>
       </c>
       <c r="AK30" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL30">
         <v>90</v>
@@ -14980,7 +14977,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR30" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS30">
         <v>858</v>
@@ -15051,25 +15048,25 @@
         <v>223</v>
       </c>
       <c r="E31" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G31" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H31" t="s">
         <v>277</v>
       </c>
       <c r="I31" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J31">
-        <v>37.2</v>
+        <v>38.8</v>
       </c>
       <c r="K31">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="L31">
         <v>5</v>
@@ -15147,7 +15144,7 @@
         <v>12.5</v>
       </c>
       <c r="AK31" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AL31">
         <v>135</v>
@@ -15168,7 +15165,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS31">
         <v>858</v>
@@ -15239,25 +15236,25 @@
         <v>223</v>
       </c>
       <c r="E32" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F32" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G32" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H32" t="s">
         <v>277</v>
       </c>
       <c r="I32" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J32">
-        <v>37.2</v>
+        <v>38.8</v>
       </c>
       <c r="K32">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -15335,7 +15332,7 @@
         <v>13.9</v>
       </c>
       <c r="AK32" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AL32">
         <v>135</v>
@@ -15356,7 +15353,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS32">
         <v>858</v>
@@ -15427,25 +15424,25 @@
         <v>223</v>
       </c>
       <c r="E33" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F33" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G33" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H33" t="s">
         <v>277</v>
       </c>
       <c r="I33" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J33">
-        <v>37.2</v>
+        <v>38.8</v>
       </c>
       <c r="K33">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -15523,7 +15520,7 @@
         <v>14.1</v>
       </c>
       <c r="AK33" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AL33">
         <v>135</v>
@@ -15544,7 +15541,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS33">
         <v>858</v>
@@ -15615,25 +15612,25 @@
         <v>224</v>
       </c>
       <c r="E34" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F34" t="s">
         <v>211</v>
       </c>
       <c r="G34" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H34" t="s">
         <v>278</v>
       </c>
       <c r="I34" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J34">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="K34">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="L34">
         <v>5</v>
@@ -15711,7 +15708,7 @@
         <v>14.4</v>
       </c>
       <c r="AK34" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AL34">
         <v>225</v>
@@ -15732,7 +15729,7 @@
         <v>1.1171</v>
       </c>
       <c r="AR34" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS34">
         <v>2916</v>
@@ -15771,7 +15768,7 @@
         <v>285</v>
       </c>
       <c r="BE34">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="BF34" t="s">
         <v>285</v>
@@ -15803,25 +15800,25 @@
         <v>224</v>
       </c>
       <c r="E35" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F35" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G35" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H35" t="s">
         <v>278</v>
       </c>
       <c r="I35" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J35">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="K35">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -15899,7 +15896,7 @@
         <v>14.7</v>
       </c>
       <c r="AK35" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AL35">
         <v>225</v>
@@ -15920,7 +15917,7 @@
         <v>1.1125</v>
       </c>
       <c r="AR35" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS35">
         <v>3069</v>
@@ -15991,25 +15988,25 @@
         <v>224</v>
       </c>
       <c r="E36" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F36" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G36" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H36" t="s">
         <v>278</v>
       </c>
       <c r="I36" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J36">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="K36">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="L36">
         <v>5</v>
@@ -16087,7 +16084,7 @@
         <v>14.6</v>
       </c>
       <c r="AK36" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AL36">
         <v>225</v>
@@ -16108,7 +16105,7 @@
         <v>1.1116</v>
       </c>
       <c r="AR36" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS36">
         <v>3103</v>
@@ -16179,25 +16176,25 @@
         <v>224</v>
       </c>
       <c r="E37" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F37" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G37" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H37" t="s">
         <v>278</v>
       </c>
       <c r="I37" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J37">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="K37">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="L37">
         <v>5</v>
@@ -16275,7 +16272,7 @@
         <v>14.4</v>
       </c>
       <c r="AK37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AL37">
         <v>247.5</v>
@@ -16296,7 +16293,7 @@
         <v>1.11</v>
       </c>
       <c r="AR37" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS37">
         <v>3153</v>
@@ -16367,25 +16364,25 @@
         <v>225</v>
       </c>
       <c r="E38" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F38" t="s">
         <v>211</v>
       </c>
       <c r="G38" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H38" t="s">
         <v>279</v>
       </c>
       <c r="I38" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J38">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="K38">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="L38">
         <v>5</v>
@@ -16463,7 +16460,7 @@
         <v>14.3</v>
       </c>
       <c r="AK38" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL38">
         <v>45</v>
@@ -16484,7 +16481,7 @@
         <v>1.1538</v>
       </c>
       <c r="AR38" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS38">
         <v>1812</v>
@@ -16555,25 +16552,25 @@
         <v>225</v>
       </c>
       <c r="E39" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F39" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H39" t="s">
         <v>279</v>
       </c>
       <c r="I39" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J39">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="K39">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="L39">
         <v>5</v>
@@ -16651,7 +16648,7 @@
         <v>15.2</v>
       </c>
       <c r="AK39" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL39">
         <v>45</v>
@@ -16672,7 +16669,7 @@
         <v>1.153</v>
       </c>
       <c r="AR39" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS39">
         <v>1853</v>
@@ -16743,25 +16740,25 @@
         <v>225</v>
       </c>
       <c r="E40" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F40" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G40" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H40" t="s">
         <v>279</v>
       </c>
       <c r="I40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J40">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="K40">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -16839,7 +16836,7 @@
         <v>15.8</v>
       </c>
       <c r="AK40" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL40">
         <v>45</v>
@@ -16860,7 +16857,7 @@
         <v>1.1529</v>
       </c>
       <c r="AR40" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS40">
         <v>1865</v>
@@ -16931,25 +16928,25 @@
         <v>225</v>
       </c>
       <c r="E41" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F41" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G41" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H41" t="s">
         <v>279</v>
       </c>
       <c r="I41" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J41">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="K41">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="L41">
         <v>5</v>
@@ -17027,7 +17024,7 @@
         <v>15.7</v>
       </c>
       <c r="AK41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL41">
         <v>45</v>
@@ -17048,7 +17045,7 @@
         <v>1.1533</v>
       </c>
       <c r="AR41" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS41">
         <v>1863</v>
@@ -17119,22 +17116,22 @@
         <v>226</v>
       </c>
       <c r="E42" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F42" t="s">
         <v>212</v>
       </c>
       <c r="G42" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H42" t="s">
         <v>280</v>
       </c>
       <c r="I42" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J42">
-        <v>52.3</v>
+        <v>54</v>
       </c>
       <c r="K42">
         <v>21.3</v>
@@ -17155,7 +17152,7 @@
         <v>5.9</v>
       </c>
       <c r="Q42">
-        <v>92.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="R42">
         <v>42.3</v>
@@ -17215,7 +17212,7 @@
         <v>14.2</v>
       </c>
       <c r="AK42" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL42">
         <v>45</v>
@@ -17236,7 +17233,7 @@
         <v>1.1473</v>
       </c>
       <c r="AR42" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS42">
         <v>1963</v>
@@ -17307,22 +17304,22 @@
         <v>226</v>
       </c>
       <c r="E43" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F43" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G43" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H43" t="s">
         <v>280</v>
       </c>
       <c r="I43" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J43">
-        <v>52.3</v>
+        <v>54</v>
       </c>
       <c r="K43">
         <v>22.3</v>
@@ -17403,7 +17400,7 @@
         <v>14.3</v>
       </c>
       <c r="AK43" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL43">
         <v>45</v>
@@ -17424,7 +17421,7 @@
         <v>1.144</v>
       </c>
       <c r="AR43" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS43">
         <v>2074</v>
@@ -17495,22 +17492,22 @@
         <v>226</v>
       </c>
       <c r="E44" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F44" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G44" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H44" t="s">
         <v>280</v>
       </c>
       <c r="I44" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J44">
-        <v>52.3</v>
+        <v>54</v>
       </c>
       <c r="K44">
         <v>23.3</v>
@@ -17591,7 +17588,7 @@
         <v>14.7</v>
       </c>
       <c r="AK44" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL44">
         <v>45</v>
@@ -17612,7 +17609,7 @@
         <v>1.1428</v>
       </c>
       <c r="AR44" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS44">
         <v>2127</v>
@@ -17683,22 +17680,22 @@
         <v>226</v>
       </c>
       <c r="E45" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F45" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H45" t="s">
         <v>280</v>
       </c>
       <c r="I45" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J45">
-        <v>52.3</v>
+        <v>54</v>
       </c>
       <c r="K45">
         <v>24.3</v>
@@ -17779,7 +17776,7 @@
         <v>15.1</v>
       </c>
       <c r="AK45" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL45">
         <v>45</v>
@@ -17800,7 +17797,7 @@
         <v>1.1422</v>
       </c>
       <c r="AR45" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS45">
         <v>2146</v>
@@ -17871,22 +17868,22 @@
         <v>227</v>
       </c>
       <c r="E46" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F46" t="s">
         <v>213</v>
       </c>
       <c r="G46" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H46" t="s">
         <v>281</v>
       </c>
       <c r="I46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J46">
-        <v>147.5</v>
+        <v>149.2</v>
       </c>
       <c r="K46">
         <v>21.7</v>
@@ -17967,7 +17964,7 @@
         <v>7.3</v>
       </c>
       <c r="AK46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL46">
         <v>90</v>
@@ -17988,7 +17985,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR46" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS46">
         <v>858</v>
@@ -18059,22 +18056,22 @@
         <v>227</v>
       </c>
       <c r="E47" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F47" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G47" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H47" t="s">
         <v>281</v>
       </c>
       <c r="I47" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J47">
-        <v>147.5</v>
+        <v>149.2</v>
       </c>
       <c r="K47">
         <v>22.7</v>
@@ -18155,7 +18152,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AK47" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AL47">
         <v>135</v>
@@ -18176,7 +18173,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR47" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS47">
         <v>858</v>
@@ -18247,22 +18244,22 @@
         <v>227</v>
       </c>
       <c r="E48" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F48" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G48" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H48" t="s">
         <v>281</v>
       </c>
       <c r="I48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J48">
-        <v>147.5</v>
+        <v>149.2</v>
       </c>
       <c r="K48">
         <v>23.7</v>
@@ -18343,7 +18340,7 @@
         <v>8.5</v>
       </c>
       <c r="AK48" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AL48">
         <v>90</v>
@@ -18364,7 +18361,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR48" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS48">
         <v>858</v>
@@ -18373,7 +18370,7 @@
         <v>291</v>
       </c>
       <c r="AU48" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AV48">
         <v>55.2</v>
@@ -18435,22 +18432,22 @@
         <v>227</v>
       </c>
       <c r="E49" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F49" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G49" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H49" t="s">
         <v>281</v>
       </c>
       <c r="I49" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J49">
-        <v>147.5</v>
+        <v>149.2</v>
       </c>
       <c r="K49">
         <v>24.7</v>
@@ -18531,7 +18528,7 @@
         <v>9.1</v>
       </c>
       <c r="AK49" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AL49">
         <v>135</v>
@@ -18552,7 +18549,7 @@
         <v>1.1896</v>
       </c>
       <c r="AR49" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS49">
         <v>858</v>
@@ -18561,7 +18558,7 @@
         <v>291</v>
       </c>
       <c r="AU49" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AV49">
         <v>55.2</v>
@@ -18623,22 +18620,22 @@
         <v>228</v>
       </c>
       <c r="E50" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F50" t="s">
         <v>214</v>
       </c>
       <c r="G50" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H50" t="s">
         <v>282</v>
       </c>
       <c r="I50" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J50">
-        <v>27.8</v>
+        <v>29.4</v>
       </c>
       <c r="K50">
         <v>23.2</v>
@@ -18719,7 +18716,7 @@
         <v>13.7</v>
       </c>
       <c r="AK50" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AL50">
         <v>247.5</v>
@@ -18740,7 +18737,7 @@
         <v>1.2156</v>
       </c>
       <c r="AR50" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS50">
         <v>87</v>
@@ -18811,22 +18808,22 @@
         <v>228</v>
       </c>
       <c r="E51" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F51" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G51" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H51" t="s">
         <v>282</v>
       </c>
       <c r="I51" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J51">
-        <v>27.8</v>
+        <v>29.4</v>
       </c>
       <c r="K51">
         <v>24.2</v>
@@ -18907,7 +18904,7 @@
         <v>13</v>
       </c>
       <c r="AK51" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AL51">
         <v>247.5</v>
@@ -18928,7 +18925,7 @@
         <v>1.2154</v>
       </c>
       <c r="AR51" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS51">
         <v>93</v>
@@ -18999,22 +18996,22 @@
         <v>228</v>
       </c>
       <c r="E52" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F52" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G52" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H52" t="s">
         <v>282</v>
       </c>
       <c r="I52" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J52">
-        <v>27.8</v>
+        <v>29.4</v>
       </c>
       <c r="K52">
         <v>25.2</v>
@@ -19095,7 +19092,7 @@
         <v>12.5</v>
       </c>
       <c r="AK52" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AL52">
         <v>247.5</v>
@@ -19116,7 +19113,7 @@
         <v>1.214</v>
       </c>
       <c r="AR52" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS52">
         <v>136</v>
@@ -19187,22 +19184,22 @@
         <v>228</v>
       </c>
       <c r="E53" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F53" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G53" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H53" t="s">
         <v>282</v>
       </c>
       <c r="I53" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J53">
-        <v>27.8</v>
+        <v>29.4</v>
       </c>
       <c r="K53">
         <v>26.2</v>
@@ -19283,7 +19280,7 @@
         <v>12.8</v>
       </c>
       <c r="AK53" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AL53">
         <v>247.5</v>
@@ -19304,7 +19301,7 @@
         <v>1.2145</v>
       </c>
       <c r="AR53" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS53">
         <v>125</v>
@@ -19375,25 +19372,25 @@
         <v>229</v>
       </c>
       <c r="E54" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F54" t="s">
         <v>215</v>
       </c>
       <c r="G54" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H54" t="s">
         <v>283</v>
       </c>
       <c r="I54" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J54">
-        <v>96.3</v>
+        <v>98</v>
       </c>
       <c r="K54">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="L54">
         <v>5</v>
@@ -19471,7 +19468,7 @@
         <v>8.9</v>
       </c>
       <c r="AK54" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AL54">
         <v>202.5</v>
@@ -19492,7 +19489,7 @@
         <v>1.1354</v>
       </c>
       <c r="AR54" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS54">
         <v>2379</v>
@@ -19563,25 +19560,25 @@
         <v>229</v>
       </c>
       <c r="E55" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F55" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G55" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H55" t="s">
         <v>283</v>
       </c>
       <c r="I55" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J55">
-        <v>96.3</v>
+        <v>98</v>
       </c>
       <c r="K55">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="L55">
         <v>5</v>
@@ -19659,7 +19656,7 @@
         <v>10.1</v>
       </c>
       <c r="AK55" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AL55">
         <v>225</v>
@@ -19680,7 +19677,7 @@
         <v>1.1374</v>
       </c>
       <c r="AR55" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS55">
         <v>2316</v>
@@ -19751,25 +19748,25 @@
         <v>229</v>
       </c>
       <c r="E56" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F56" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G56" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H56" t="s">
         <v>283</v>
       </c>
       <c r="I56" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J56">
-        <v>96.3</v>
+        <v>98</v>
       </c>
       <c r="K56">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="L56">
         <v>5</v>
@@ -19847,7 +19844,7 @@
         <v>11</v>
       </c>
       <c r="AK56" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AL56">
         <v>225</v>
@@ -19868,7 +19865,7 @@
         <v>1.1417</v>
       </c>
       <c r="AR56" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS56">
         <v>2202</v>
@@ -19939,25 +19936,25 @@
         <v>229</v>
       </c>
       <c r="E57" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F57" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G57" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H57" t="s">
         <v>283</v>
       </c>
       <c r="I57" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J57">
-        <v>96.3</v>
+        <v>98</v>
       </c>
       <c r="K57">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="L57">
         <v>5</v>
@@ -19978,7 +19975,7 @@
         <v>79.3</v>
       </c>
       <c r="R57">
-        <v>75.7</v>
+        <v>75.8</v>
       </c>
       <c r="S57">
         <v>0.78</v>
@@ -20035,7 +20032,7 @@
         <v>13</v>
       </c>
       <c r="AK57" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AL57">
         <v>225</v>
@@ -20056,7 +20053,7 @@
         <v>1.1418</v>
       </c>
       <c r="AR57" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AS57">
         <v>2179</v>
@@ -20127,25 +20124,25 @@
         <v>230</v>
       </c>
       <c r="E58" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F58" t="s">
         <v>215</v>
       </c>
       <c r="G58" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H58" t="s">
         <v>284</v>
       </c>
       <c r="I58" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J58">
-        <v>148.1</v>
+        <v>149.7</v>
       </c>
       <c r="K58">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="L58">
         <v>5</v>
@@ -20223,7 +20220,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="AK58" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AL58">
         <v>270</v>
@@ -20244,7 +20241,7 @@
         <v>1.1792</v>
       </c>
       <c r="AR58" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS58">
         <v>1051</v>
@@ -20315,25 +20312,25 @@
         <v>230</v>
       </c>
       <c r="E59" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F59" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G59" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H59" t="s">
         <v>284</v>
       </c>
       <c r="I59" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J59">
-        <v>148.1</v>
+        <v>149.7</v>
       </c>
       <c r="K59">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="L59">
         <v>5</v>
@@ -20411,7 +20408,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AK59" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AL59">
         <v>270</v>
@@ -20432,7 +20429,7 @@
         <v>1.1781</v>
       </c>
       <c r="AR59" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS59">
         <v>1084</v>
@@ -20503,25 +20500,25 @@
         <v>230</v>
       </c>
       <c r="E60" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F60" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G60" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H60" t="s">
         <v>284</v>
       </c>
       <c r="I60" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J60">
-        <v>148.1</v>
+        <v>149.7</v>
       </c>
       <c r="K60">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="L60">
         <v>5</v>
@@ -20599,7 +20596,7 @@
         <v>10.2</v>
       </c>
       <c r="AK60" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AL60">
         <v>270</v>
@@ -20620,7 +20617,7 @@
         <v>1.1785</v>
       </c>
       <c r="AR60" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS60">
         <v>1075</v>
@@ -20691,25 +20688,25 @@
         <v>230</v>
       </c>
       <c r="E61" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F61" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G61" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H61" t="s">
         <v>284</v>
       </c>
       <c r="I61" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J61">
-        <v>148.1</v>
+        <v>149.7</v>
       </c>
       <c r="K61">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="L61">
         <v>5</v>
@@ -20787,7 +20784,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AK61" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AL61">
         <v>270</v>
@@ -20808,7 +20805,7 @@
         <v>1.1799</v>
       </c>
       <c r="AR61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AS61">
         <v>1034</v>
@@ -20974,10 +20971,10 @@
         <v>88.40000000000001</v>
       </c>
       <c r="G2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I2" s="4">
         <v>21</v>
@@ -20986,7 +20983,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="K2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L2">
         <v>91</v>
@@ -21030,10 +21027,10 @@
         <v>76.7</v>
       </c>
       <c r="G3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I3" s="4">
         <v>15</v>
@@ -21042,7 +21039,7 @@
         <v>6.4</v>
       </c>
       <c r="K3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="L3">
         <v>85.7</v>
@@ -21086,10 +21083,10 @@
         <v>66.8</v>
       </c>
       <c r="G4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I4" s="4">
         <v>9</v>
@@ -21098,7 +21095,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L4">
         <v>91.09999999999999</v>
@@ -21142,10 +21139,10 @@
         <v>62</v>
       </c>
       <c r="G5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I5" s="4">
         <v>7</v>
@@ -21154,7 +21151,7 @@
         <v>2.9</v>
       </c>
       <c r="K5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L5">
         <v>87.5</v>
@@ -21198,10 +21195,10 @@
         <v>56.5</v>
       </c>
       <c r="G6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I6" s="4">
         <v>4</v>
@@ -21254,10 +21251,10 @@
         <v>56.2</v>
       </c>
       <c r="G7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I7" s="4">
         <v>3</v>
@@ -21266,7 +21263,7 @@
         <v>1.5</v>
       </c>
       <c r="K7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L7">
         <v>86.09999999999999</v>
@@ -21310,10 +21307,10 @@
         <v>54.9</v>
       </c>
       <c r="G8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I8" s="4">
         <v>3</v>
@@ -21322,7 +21319,7 @@
         <v>1.2</v>
       </c>
       <c r="K8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L8">
         <v>93.90000000000001</v>
@@ -21366,10 +21363,10 @@
         <v>54.5</v>
       </c>
       <c r="G9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I9" s="4">
         <v>2</v>
@@ -21378,7 +21375,7 @@
         <v>1.1</v>
       </c>
       <c r="K9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L9">
         <v>86.59999999999999</v>
@@ -21422,10 +21419,10 @@
         <v>54.3</v>
       </c>
       <c r="G10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I10" s="4">
         <v>2</v>
@@ -21434,7 +21431,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L10">
         <v>81.90000000000001</v>
@@ -21478,10 +21475,10 @@
         <v>48.9</v>
       </c>
       <c r="G11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I11" s="4">
         <v>-1</v>
@@ -21490,7 +21487,7 @@
         <v>-0.3</v>
       </c>
       <c r="K11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L11">
         <v>87.40000000000001</v>
@@ -21534,10 +21531,10 @@
         <v>47.2</v>
       </c>
       <c r="G12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I12" s="4">
         <v>-2</v>
@@ -21546,7 +21543,7 @@
         <v>-0.7</v>
       </c>
       <c r="K12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L12">
         <v>84.40000000000001</v>
@@ -21590,10 +21587,10 @@
         <v>44.8</v>
       </c>
       <c r="G13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I13" s="4">
         <v>-3</v>
@@ -21602,7 +21599,7 @@
         <v>-1.2</v>
       </c>
       <c r="K13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L13">
         <v>93.59999999999999</v>
@@ -21646,10 +21643,10 @@
         <v>42.9</v>
       </c>
       <c r="G14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I14" s="4">
         <v>-4</v>
@@ -21658,7 +21655,7 @@
         <v>-1.7</v>
       </c>
       <c r="K14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L14">
         <v>86.3</v>
@@ -21702,10 +21699,10 @@
         <v>42.3</v>
       </c>
       <c r="G15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I15" s="4">
         <v>-4</v>
@@ -21714,7 +21711,7 @@
         <v>-1.8</v>
       </c>
       <c r="K15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L15">
         <v>91.2</v>
@@ -21758,10 +21755,10 @@
         <v>42</v>
       </c>
       <c r="G16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I16" s="4">
         <v>-4</v>
@@ -21770,7 +21767,7 @@
         <v>-1.9</v>
       </c>
       <c r="K16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L16">
         <v>84.90000000000001</v>
